--- a/AAII_Financials/Quarterly/MGYOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MGYOY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
   <si>
     <t>MGYOY</t>
   </si>
@@ -656,97 +656,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="21" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="22" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -783,29 +787,32 @@
       <c r="N8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="3">
         <v>7204000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7846600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6767500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5235000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4713500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4611500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4054100</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -842,29 +849,32 @@
       <c r="N9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3">
         <v>5444300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5708800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4745800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3847800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3447500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3303800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2874900</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -901,29 +911,32 @@
       <c r="N10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="3">
         <v>1759700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2137800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2021700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1387200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1266000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1307700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1179200</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -945,8 +958,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1004,8 +1018,11 @@
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,8 +1080,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1101,8 +1121,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1122,8 +1142,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1160,29 +1183,32 @@
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="3">
         <v>505200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>348700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>298100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>174900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>419800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>293500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>329300</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,8 +1227,9 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1239,29 +1266,32 @@
       <c r="N17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="3">
         <v>6589900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6630800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5764500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4606400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4296000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4102500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3650600</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1298,29 +1328,32 @@
       <c r="N18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="3">
         <v>614100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1215800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1003000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>628600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>417500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>509000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>403500</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,8 +1375,9 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1380,29 +1414,32 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3">
         <v>-73500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-163000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-52100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>8000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-9700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-80300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>76800</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1439,29 +1476,32 @@
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>1045800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1397800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1242800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>764200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>836400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>749000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>834900</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1498,8 +1538,8 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1519,8 +1559,11 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1557,29 +1600,32 @@
       <c r="N23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="3">
         <v>540600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1052800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>950900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>636600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>407800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>428700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>480300</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1616,29 +1662,32 @@
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="3">
         <v>672700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>248900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>172800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>103100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>53800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-60300</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,8 +1745,11 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1734,29 +1786,32 @@
       <c r="N26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="3">
         <v>-132100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>803900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>750300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>463800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>304700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>374900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>540600</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1793,29 +1848,32 @@
       <c r="N27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="3">
         <v>-62200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>716700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>684800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>380700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>302200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>340100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>511500</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1911,29 +1972,32 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3">
         <v>260400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>78100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>133400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>147400</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>14300</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>56700</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,8 +2117,11 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2088,29 +2158,32 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3">
         <v>73500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>163000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>52100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-8000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>9700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>80300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-76800</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2147,29 +2220,32 @@
       <c r="N33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P33" s="3">
         <v>198200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>794900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>818200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>528100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>316500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>396800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>533400</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,8 +2303,11 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2265,93 +2344,99 @@
       <c r="N35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P35" s="3">
         <v>198200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>794900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>818200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>528100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>316500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>396800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>533400</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,539 +2482,567 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1378300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1102700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1021800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1091200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>791500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1193400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1251000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1586600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2112600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>991700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1251000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1456500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1672600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1649300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2204100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1371100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1047200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>961200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>811100</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>277500</v>
+      </c>
+      <c r="E42" s="3">
         <v>561100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>61500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>49000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>32600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>100100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>318800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>332300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>113900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>318500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>318800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>760800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>508600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>338800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>424100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>368700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>172100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>167500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>120400</v>
       </c>
     </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4029300</v>
+      </c>
+      <c r="E43" s="3">
         <v>2767400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3584300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2687300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3068000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2863000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2598200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2536000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3226700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3188900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2598200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2635600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2673500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3398800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3366600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3087200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2174600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2226300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2064000</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3198700</v>
+      </c>
+      <c r="E44" s="3">
         <v>2384700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2459200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2215900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2396600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2400200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2333500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2657600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2721700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2425300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2333500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2431300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2801700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3249700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2839700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2419100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2003000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1721200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1727500</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1011700</v>
+      </c>
+      <c r="E45" s="3">
         <v>637000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>654200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>119200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>171400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>191700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>214300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>347800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>808300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>492200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>214300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>363600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>383600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>791000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>748100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>624900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>281100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>207600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>235100</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10425200</v>
+      </c>
+      <c r="E46" s="3">
         <v>7852600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8138400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6443900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6735300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7052400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6904300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7626500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9184500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7416600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6904300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7647700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8040000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9427600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9582600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7871000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5678000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5283800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4958100</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1615300</v>
+      </c>
+      <c r="E47" s="3">
         <v>1563000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1430900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1290500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1221800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1270500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1239300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1160100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1139000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1483300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1239300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1430500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1471200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1623800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1403600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1243900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1249300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1160900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1082700</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13660300</v>
+      </c>
+      <c r="E48" s="3">
         <v>13850100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12789900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11964700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11488600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11553000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10858100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10176400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9571200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10612000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10858100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10602000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10754800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10467100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9991200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9414500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9649300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9213200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9095900</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1340200</v>
+      </c>
+      <c r="E49" s="3">
         <v>967200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1441400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>996400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1304600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1518800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1632700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1472900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1157300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1604500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1632700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1511200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1552800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1309500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1207500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1212400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1247800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1106200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1077200</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,67 +3162,73 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>325100</v>
+      </c>
+      <c r="E52" s="3">
         <v>303100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>339900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>253300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>278900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>272800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>253300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>273300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>253400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>239300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>253300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>269900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>570400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>589100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>615400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>551900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>712300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>738900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>733000</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,67 +3286,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27899200</v>
+      </c>
+      <c r="E54" s="3">
         <v>25043400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>24571600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21325800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21591000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22260800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21497800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21237600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21853000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21775700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21497800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21787000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>22389200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>23417000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>22800300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>20293800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>18536900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17503000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>16946900</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,362 +3398,381 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3123000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2462000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2662600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2268400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2427900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2779900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2015800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2669800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2776900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2776800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2015800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2165000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2814600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2904500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2897300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2708000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2417500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1890000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2016700</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1000900</v>
+      </c>
+      <c r="E58" s="3">
         <v>1165700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>815000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>730400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>867600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>535800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>333300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1249300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1450500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>505900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>333300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>943400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1317000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1470500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1513400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>478800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>529000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>998600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>929900</v>
       </c>
     </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2680100</v>
+      </c>
+      <c r="E59" s="3">
         <v>1691200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1572100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1034600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>472600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1173400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2222600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1967300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2551100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2419200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2222600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3185600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2984100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3019700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3674100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2777400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1786500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1856300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1866100</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8204000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6266300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6163000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4815700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4849100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5325700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5798700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6749700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7748800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5701900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5798700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6293900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7115700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7394700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8084700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5964100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4733000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4744900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4812700</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2427200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1999600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2367200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2424000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2776500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2639900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2394500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1732100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2303900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2529700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2394500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1794700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1827700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2014500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2402800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3015100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2469500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2072700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2097700</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2352900</v>
+      </c>
+      <c r="E62" s="3">
         <v>2114900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2213400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1730400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1635400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1549900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1787000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1565100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1855400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1830400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1787000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1802400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2171700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2506700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2388000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2215700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2633300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2452800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2415300</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,67 +3954,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13598100</v>
+      </c>
+      <c r="E66" s="3">
         <v>11098300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11350400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9600600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9762500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10131200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10441200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10543400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12340600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10435000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10441200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10251500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12179500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13043900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13857200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12104600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10622000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10106900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10111000</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4058,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,67 +4288,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10672800</v>
+      </c>
+      <c r="E72" s="3">
         <v>9979400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9285200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7907100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8210600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8564400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7750800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7087400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6017400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10144400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7750800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8091900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7471800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10156600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6278200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7971900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5636300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7173300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4954000</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,67 +4536,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13101800</v>
+      </c>
+      <c r="E76" s="3">
         <v>12685100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12067800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10679400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10854600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11088300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10096100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9684600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8571500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10359900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10096100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10527700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10209800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10373100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8943100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8189200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7914900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7396100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6835900</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,72 +4660,78 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4573,29 +4768,32 @@
       <c r="N81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P81" s="3">
         <v>198200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>794900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>818200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>528100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>316500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>396800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>533400</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,67 +4815,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>311000</v>
+      </c>
+      <c r="E83" s="3">
         <v>227700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>264300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>497300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>285700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>139800</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3">
         <v>240500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>292300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>285700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>139800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>505200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>345000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>274100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>145400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>428700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>320300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>354500</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,67 +5185,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1282900</v>
+      </c>
+      <c r="E89" s="3">
         <v>661200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>688700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>732100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>435800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>733400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>28500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1677400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>929800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>606600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>28500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>766100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1768400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1127200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>969700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-12600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>857100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>669300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>985500</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,67 +5273,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-309400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-697700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-266100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-531800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-323100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-592300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-268700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-558400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-337900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-329900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-268700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-243900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-209508000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-159144000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-128193000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-119077000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-186252000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-104505000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-110081000</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,67 +5457,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-590600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1210600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-260500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-445300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-269200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-466300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-183300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1146100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-383100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-164600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-183300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-571000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1208300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-446900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-371300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-347600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-513900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-291100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-297100</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,53 +5545,54 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>300</v>
+      </c>
+      <c r="E96" s="3">
         <v>100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>626600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>529500</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>100</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>624500</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-523900</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -5366,13 +5600,16 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-180100</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,181 +5791,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-289000</v>
+      </c>
+      <c r="E100" s="3">
         <v>182800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-289100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>37900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-449500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-61700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>13700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-375200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>133400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-731800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>13700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-311900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-395600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1458200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>110800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>696800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-272600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-236700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-285100</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-79900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-97500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-177400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>135200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>27700</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3">
         <v>-7000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>183000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>135200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>27700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-187000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>216100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>141000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>25300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>25800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>9300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>342500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-381500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>61200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>400100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-285700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>125500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-238700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-21200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>815300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-178600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-238700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-249200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-22400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-561800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>850600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>361600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>96400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>150800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>392100</v>
       </c>
     </row>
